--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -29,52 +29,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>对账单号</t>
+  </si>
+  <si>
+    <t>物流商</t>
+  </si>
+  <si>
+    <t>单据状态</t>
+  </si>
   <si>
     <t>物流跟踪号</t>
   </si>
   <si>
-    <t>业务单号</t>
-  </si>
-  <si>
-    <t>关联单号</t>
-  </si>
-  <si>
-    <t>店铺</t>
-  </si>
-  <si>
-    <t>发货国家</t>
-  </si>
-  <si>
-    <t>目的国家</t>
+    <t>货件单号</t>
   </si>
   <si>
     <t>签收日期</t>
   </si>
   <si>
-    <t>运输状态</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>计费方式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>类型</t>
-    </r>
+    <t>计费方式</t>
+  </si>
+  <si>
+    <t>类型</t>
   </si>
   <si>
     <t>总物流费用</t>
@@ -98,36 +76,27 @@
     <t>其他费用(总)</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>对账状态</t>
   </si>
   <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.logisticsSupplierName}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
     <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
   </si>
   <si>
-    <t>{.relationCode}</t>
-  </si>
-  <si>
-    <t>{.shopName}</t>
-  </si>
-  <si>
-    <t>{.fromCountryName}</t>
-  </si>
-  <si>
-    <t>{.toCountryName}</t>
-  </si>
-  <si>
     <t>{.receiveDate}</t>
   </si>
   <si>
-    <t>{.transportStatusName}</t>
-  </si>
-  <si>
     <t>{.billingMethodName}</t>
   </si>
   <si>
@@ -137,25 +106,22 @@
     <t>{.totalLogisticsCost}</t>
   </si>
   <si>
-    <t>{.actualWeightShow}</t>
-  </si>
-  <si>
-    <t>{.volumeWeightShow}</t>
-  </si>
-  <si>
-    <t>{.billingWeightShow}</t>
-  </si>
-  <si>
-    <t>{.shippingCostShow}</t>
-  </si>
-  <si>
-    <t>{.declareCostShow}</t>
-  </si>
-  <si>
-    <t>{.otherCostShow}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
+    <t>{.actualWeight}</t>
+  </si>
+  <si>
+    <t>{.volumeWeight}</t>
+  </si>
+  <si>
+    <t>{.billingWeight}</t>
+  </si>
+  <si>
+    <t>{.shippingCost}</t>
+  </si>
+  <si>
+    <t>{.declareCost}</t>
+  </si>
+  <si>
+    <t>{.otherCost}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -171,7 +137,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,9 +146,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -650,141 +621,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1098,26 +1072,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="4" width="14.875" customWidth="1"/>
-    <col min="5" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="8" width="19.125" customWidth="1"/>
-    <col min="9" max="11" width="17.125" customWidth="1"/>
-    <col min="12" max="12" width="19.625" customWidth="1"/>
-    <col min="13" max="13" width="17.125" customWidth="1"/>
-    <col min="14" max="14" width="16.375" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="17.125" customWidth="1"/>
-    <col min="18" max="18" width="12.875" customWidth="1"/>
-    <col min="19" max="19" width="16.125" customWidth="1"/>
+    <col min="1" max="1" width="8.75" customWidth="1"/>
+    <col min="2" max="4" width="14.75" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="8" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="17.125" customWidth="1"/>
+    <col min="12" max="12" width="20.125" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="17.125" customWidth="1"/>
+    <col min="16" max="16" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1133,19 +1106,19 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1166,73 +1139,55 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26205" windowHeight="7740"/>
+    <workbookView windowWidth="26205" windowHeight="7995"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <t>单据状态</t>
   </si>
   <si>
-    <t>物流跟踪号</t>
+    <t>物流运单号</t>
   </si>
   <si>
     <t>货件单号</t>
@@ -88,7 +88,7 @@
     <t>{.approveStatusName}</t>
   </si>
   <si>
-    <t>{.trackNo}</t>
+    <t>{.transportNo}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26205" windowHeight="7995"/>
+    <workbookView windowWidth="24975" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,13 +106,13 @@
     <t>{.totalLogisticsCost}</t>
   </si>
   <si>
-    <t>{.actualWeight}</t>
-  </si>
-  <si>
-    <t>{.volumeWeight}</t>
-  </si>
-  <si>
-    <t>{.billingWeight}</t>
+    <t>{.actualWeightWithUnit}</t>
+  </si>
+  <si>
+    <t>{.volumeWeightWithUnit}</t>
+  </si>
+  <si>
+    <t>{.billingWeightWithUnit}</t>
   </si>
   <si>
     <t>{.shippingCost}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -1080,7 +1080,8 @@
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
     <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="9" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="22.75" customWidth="1"/>
     <col min="10" max="10" width="19.625" customWidth="1"/>
     <col min="11" max="11" width="17.125" customWidth="1"/>
     <col min="12" max="12" width="20.125" customWidth="1"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24975" windowHeight="7635"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>对账单号</t>
   </si>
@@ -76,6 +76,9 @@
     <t>其他费用(总)</t>
   </si>
   <si>
+    <t>对账类型</t>
+  </si>
+  <si>
     <t>对账状态</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t>{.otherCost}</t>
+  </si>
+  <si>
+    <t>{.reconciliationCountName}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -1072,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -1087,11 +1093,11 @@
     <col min="12" max="12" width="20.125" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="15" max="16" width="17.125" customWidth="1"/>
+    <col min="17" max="17" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1140,55 +1146,61 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsFirstMileReconciliationDetail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>对账单号</t>
   </si>
@@ -73,6 +73,9 @@
     <t>报关费用(总)</t>
   </si>
   <si>
+    <t>其他税费(总)</t>
+  </si>
+  <si>
     <t>其他费用(总)</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t>{.declareCost}</t>
+  </si>
+  <si>
+    <t>{.otherTaxCost}</t>
   </si>
   <si>
     <t>{.otherCost}</t>
@@ -1078,7 +1084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -1094,10 +1100,11 @@
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
     <col min="15" max="16" width="17.125" customWidth="1"/>
-    <col min="17" max="17" width="16.125" customWidth="1"/>
+    <col min="17" max="17" width="24.875" customWidth="1"/>
+    <col min="18" max="18" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1149,58 +1156,64 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
